--- a/vocexcel/templates/VocExcel-template-100.xlsx
+++ b/vocexcel/templates/VocExcel-template-100.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/kurrawong/VocExcel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/kurrawong/VocExcel/vocexcel/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9EBD9E0-BE28-4F41-A132-4B85016C5727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C311290-424F-504C-BF02-26C1874758E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44840" yWindow="1000" windowWidth="53660" windowHeight="27680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,11 +1730,6 @@
     <t>Broader Concept IRI</t>
   </si>
   <si>
-    <t xml:space="preserve">Select the IRI of a concept that is the broader (parent) concept of this one.
-Concepts that have no broader concept indicated are assumed to be top concepts of the vocabulary.
-If you want multiple parents for a Concept, </t>
-  </si>
-  <si>
     <t>Additional Broader Concept IRI</t>
   </si>
   <si>
@@ -1773,6 +1768,11 @@
   </si>
   <si>
     <t>Geological Survey of South Australia</t>
+  </si>
+  <si>
+    <t>Select the IRI of a concept that is the broader (parent) concept of this one.
+Concepts that have no broader concept indicated are assumed to be top concepts of the vocabulary.
+If you want multiple parents for a Concept, add the second and subsequent parents to the Additional Concept Properties sheet</t>
   </si>
 </sst>
 </file>
@@ -2204,21 +2204,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2239,6 +2224,21 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2462,252 +2462,252 @@
   <dimension ref="A1:K985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="61"/>
-    <col min="2" max="2" width="68.1640625" style="62" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="61"/>
-    <col min="4" max="4" width="24" style="62" customWidth="1"/>
-    <col min="5" max="9" width="12.5" style="61"/>
-    <col min="10" max="10" width="21.33203125" style="61" customWidth="1"/>
-    <col min="11" max="24" width="12.5" style="61"/>
-    <col min="25" max="25" width="12.5" style="61" customWidth="1"/>
-    <col min="26" max="26" width="9.6640625" style="61" customWidth="1"/>
-    <col min="27" max="16384" width="12.5" style="61"/>
+    <col min="1" max="1" width="12.5" style="56"/>
+    <col min="2" max="2" width="68.1640625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="56"/>
+    <col min="4" max="4" width="24" style="57" customWidth="1"/>
+    <col min="5" max="9" width="12.5" style="56"/>
+    <col min="10" max="10" width="21.33203125" style="56" customWidth="1"/>
+    <col min="11" max="24" width="12.5" style="56"/>
+    <col min="25" max="25" width="12.5" style="56" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" style="56" customWidth="1"/>
+    <col min="27" max="16384" width="12.5" style="56"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="252" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.15">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="64" t="s">
+      <c r="C4" s="58"/>
+      <c r="D4" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+    </row>
+    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.15">
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="60" t="s">
         <v>216</v>
       </c>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-    </row>
-    <row r="5" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A5" s="63"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A6" s="63"/>
-      <c r="B6" s="64" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A7" s="63"/>
-      <c r="B7" s="66" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="64" t="s">
+      <c r="C7" s="58"/>
+      <c r="D7" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="E7" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="67"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="62"/>
     </row>
     <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.15">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64" t="s">
+      <c r="A9" s="58"/>
+      <c r="B9" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A10" s="63"/>
-      <c r="B10" s="66" t="s">
+      <c r="A10" s="58"/>
+      <c r="B10" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.15">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:11" ht="41" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64" t="s">
+      <c r="A12" s="58"/>
+      <c r="B12" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="61"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="56"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A13" s="63"/>
-      <c r="B13" s="66" t="s">
+      <c r="A13" s="58"/>
+      <c r="B13" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="63"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A15" s="63"/>
-      <c r="B15" s="64" t="s">
+      <c r="A15" s="58"/>
+      <c r="B15" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
     </row>
     <row r="16" spans="1:11" ht="19" x14ac:dyDescent="0.15">
-      <c r="A16" s="63"/>
-      <c r="B16" s="66" t="s">
+      <c r="A16" s="58"/>
+      <c r="B16" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="19" x14ac:dyDescent="0.15">
-      <c r="A17" s="63"/>
-      <c r="B17" s="66" t="s">
+      <c r="A17" s="58"/>
+      <c r="B17" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="63"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.15">
-      <c r="A18" s="63"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="19" x14ac:dyDescent="0.15">
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="59" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19" x14ac:dyDescent="0.15">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="61" t="s">
         <v>166</v>
       </c>
     </row>
@@ -4101,12 +4101,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" x14ac:dyDescent="0.15">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="2" spans="1:4" s="35" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
@@ -4283,7 +4283,7 @@
         <v>171</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D16" s="33" t="s">
         <v>113</v>
@@ -7302,16 +7302,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
     </row>
     <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.15">
       <c r="A2" s="31" t="s">
@@ -7365,7 +7365,7 @@
         <v>105</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F3" s="26" t="s">
         <v>130</v>
@@ -10567,16 +10567,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
@@ -10604,12 +10604,12 @@
         <v>117</v>
       </c>
       <c r="I2" s="53" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:27" s="20" customFormat="1" ht="273" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>150</v>
@@ -10633,7 +10633,7 @@
         <v>115</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J3" s="45"/>
       <c r="K3" s="45"/>
@@ -20692,13 +20692,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -20726,10 +20726,10 @@
         <v>129</v>
       </c>
       <c r="D3" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="49" t="s">
         <v>213</v>
-      </c>
-      <c r="E3" s="49" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="20" customFormat="1" ht="18" x14ac:dyDescent="0.15">
@@ -22077,11 +22077,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="24" t="s">
@@ -22182,11 +22182,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
     </row>
     <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
@@ -22227,7 +22227,7 @@
         <v>173</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -22241,7 +22241,7 @@
         <v>174</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -22252,7 +22252,7 @@
         <v>175</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -22409,15 +22409,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006CE8352A0AF1CD4AB9B3521FB05BB06E" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ad776eddaa4c2424eb5fa9eef7239753">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bcd33c6e-30cb-4633-b8ec-d716de95c77b" xmlns:ns3="cc9fd5b5-cf46-4eda-9201-7118bc1c1603" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c03cb13ad1de5dce1c8a6420670aeaf6" ns2:_="" ns3:_="">
     <xsd:import namespace="bcd33c6e-30cb-4633-b8ec-d716de95c77b"/>
@@ -22654,15 +22645,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41C0741D-72E1-4141-9700-3202E4B56A5A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C5B03A-DD20-4DDE-9069-342AD74757E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22679,4 +22671,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41C0741D-72E1-4141-9700-3202E4B56A5A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>